--- a/branches/fix/examplescenario-instances/ValueSet-mii-vs-dokument-fachgebiet.xlsx
+++ b/branches/fix/examplescenario-instances/ValueSet-mii-vs-dokument-fachgebiet.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T18:07:30+00:00</t>
+    <t>2026-09-09T18:13:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/examplescenario-instances/ValueSet-mii-vs-dokument-fachgebiet.xlsx
+++ b/branches/fix/examplescenario-instances/ValueSet-mii-vs-dokument-fachgebiet.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T18:13:45+00:00</t>
+    <t>2026-09-09T18:45:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/examplescenario-instances/ValueSet-mii-vs-dokument-fachgebiet.xlsx
+++ b/branches/fix/examplescenario-instances/ValueSet-mii-vs-dokument-fachgebiet.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T18:45:51+00:00</t>
+    <t>2026-09-11T08:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
